--- a/laporan_padel_dki_jakarta_2026-10-01.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-01.xlsx
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.054.000</t>
+          <t>Rp2.230.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp2.280.000</t>
+          <t>Rp2.085.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp1.660.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp650.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-01.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-01.xlsx
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.230.000</t>
+          <t>Rp2.494.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.396.000</t>
+          <t>Rp896.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.500.000</t>
+          <t>Rp5.350.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.625.000</t>
+          <t>Rp3.375.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.925.000</t>
+          <t>Rp1.575.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.170.000</t>
+          <t>Rp1.510.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>112</v>
       </c>
       <c r="D61" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp1.596.000</t>
+          <t>Rp1.396.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>68</v>
       </c>
       <c r="D63" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp2.210.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>176</v>
       </c>
       <c r="D70" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp996.000</t>
+          <t>Rp1.494.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp1.015.000</t>
+          <t>Rp1.355.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>120</v>
       </c>
       <c r="D78" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp4.410.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2897,14 +2897,14 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="D80" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp500.000</t>
+          <t>Rp50.000 - Rp500.000</t>
         </is>
       </c>
     </row>
@@ -2931,16 +2931,16 @@
         <v>80</v>
       </c>
       <c r="D81" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp2.989.000</t>
+          <t>Rp3.188.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>80</v>
       </c>
       <c r="D88" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp896.000</t>
+          <t>Rp1.095.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp200.000</t>
+          <t>Rp150.000 - Rp240.000</t>
         </is>
       </c>
     </row>
@@ -3571,16 +3571,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.053.000</t>
+          <t>Rp1.215.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>127</v>
       </c>
       <c r="D3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp14.847.000</t>
+          <t>Rp15.082.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp12.750.000</t>
+          <t>Rp13.250.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>85</v>
       </c>
       <c r="D6" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp3.310.000</t>
+          <t>Rp360.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.450.000</t>
+          <t>Rp6.050.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>84</v>
       </c>
       <c r="D49" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>72</v>
       </c>
       <c r="D53" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp720.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>75</v>
       </c>
       <c r="D56" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp124.000</t>
+          <t>Rp257.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>64</v>
       </c>
       <c r="D62" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp8.400.000</t>
+          <t>Rp9.000.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>144</v>
       </c>
       <c r="D66" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp14.150.000</t>
+          <t>Rp15.050.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>30</v>
       </c>
       <c r="D67" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp1.225.000</t>
+          <t>Rp975.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>30</v>
       </c>
       <c r="D68" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp4.620.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.775.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.000.000</t>
+          <t>Rp7.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp8.375.000</t>
+          <t>Rp8.610.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp6.070.000</t>
+          <t>Rp6.075.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp12.085.000</t>
+          <t>Rp12.310.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>102</v>
       </c>
       <c r="D9" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.283.000</t>
+          <t>Rp8.442.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp17.661.000</t>
+          <t>Rp16.531.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>16</v>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp859.000</t>
+          <t>Rp1.019.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp6.694.000</t>
+          <t>Rp6.296.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp3.650.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.775.000</t>
+          <t>Rp2.235.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp9.225.000</t>
+          <t>Rp9.325.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>80</v>
       </c>
       <c r="D41" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.175.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.800.000</t>
+          <t>Rp6.050.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp270.000</t>
+          <t>Rp540.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp6.160.000</t>
+          <t>Rp5.899.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp3.360.000</t>
+          <t>Rp3.930.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.932.000</t>
+          <t>Rp2.031.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp632.000</t>
+          <t>Rp970.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-01.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-01.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.840.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp3.050.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp896.000</t>
+          <t>Rp995.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp11.145.000</t>
+          <t>Rp11.395.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp10.874.000</t>
+          <t>Rp10.324.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -944,24 +944,24 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>134</v>
       </c>
       <c r="D17" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp5.340.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp150.000</t>
+          <t>Rp70.000 - Rp150.000</t>
         </is>
       </c>
     </row>
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.185.000</t>
+          <t>Rp4.365.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp2.157.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.350.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.375.000</t>
+          <t>Rp3.125.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp1.450.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1288,16 +1288,16 @@
         <v>36</v>
       </c>
       <c r="D28" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp298.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.196.000</t>
+          <t>Rp3.696.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.974.000</t>
+          <t>Rp3.220.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.170.000</t>
+          <t>Rp1.560.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>180</v>
       </c>
       <c r="D43" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp14.850.000</t>
+          <t>Rp15.100.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>96</v>
       </c>
       <c r="D48" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.371.000</t>
+          <t>Rp4.569.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>84</v>
       </c>
       <c r="D51" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp2.394.000</t>
+          <t>Rp2.944.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>60</v>
       </c>
       <c r="D54" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp1.496.000</t>
+          <t>Rp1.408.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>17</v>
       </c>
       <c r="D56" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp447.000</t>
+          <t>Rp298.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>48</v>
       </c>
       <c r="D57" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>54</v>
       </c>
       <c r="D58" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp860.000</t>
+          <t>Rp925.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp2.175.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>112</v>
       </c>
       <c r="D61" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp1.396.000</t>
+          <t>Rp1.993.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp7.160.000</t>
+          <t>Rp8.060.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>90</v>
       </c>
       <c r="D67" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp7.546.000</t>
+          <t>Rp8.344.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>176</v>
       </c>
       <c r="D70" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp1.494.000</t>
+          <t>Rp1.743.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>120</v>
       </c>
       <c r="D78" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp4.410.000</t>
+          <t>Rp4.900.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>80</v>
       </c>
       <c r="D88" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp1.095.000</t>
+          <t>Rp1.842.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>90</v>
       </c>
       <c r="D90" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.640.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp2.160.000</t>
+          <t>Rp2.670.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>127</v>
       </c>
       <c r="D3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.082.000</t>
+          <t>Rp15.317.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.198.000</t>
+          <t>Rp2.297.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp7.415.000</t>
+          <t>Rp7.985.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp449.000</t>
+          <t>Rp624.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp11.150.000</t>
+          <t>Rp12.050.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp15.685.000</t>
+          <t>Rp16.035.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.760.000</t>
+          <t>Rp2.890.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>28</v>
       </c>
       <c r="D36" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp905.000</t>
+          <t>Rp1.094.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp14.100.000</t>
+          <t>Rp17.100.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>54</v>
       </c>
       <c r="D44" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4935,16 +4935,16 @@
         <v>6</v>
       </c>
       <c r="D46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4966,16 +4966,16 @@
         <v>32</v>
       </c>
       <c r="D47" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp2.324.000</t>
+          <t>Rp2.988.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>84</v>
       </c>
       <c r="D49" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>72</v>
       </c>
       <c r="D50" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp2.676.000</t>
+          <t>Rp4.260.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>54</v>
       </c>
       <c r="D51" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp6.900.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>90</v>
       </c>
       <c r="D63" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp9.050.000</t>
+          <t>Rp9.450.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>144</v>
       </c>
       <c r="D66" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp15.050.000</t>
+          <t>Rp15.500.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>30</v>
       </c>
       <c r="D67" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp975.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>30</v>
       </c>
       <c r="D68" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp4.620.000</t>
+          <t>Rp3.080.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp20.075.000</t>
+          <t>Rp20.955.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.775.000</t>
+          <t>Rp2.025.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.500.000</t>
+          <t>Rp8.900.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6133,21 +6133,21 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp6.075.000</t>
+          <t>Rp4.890.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rp190.000 - Rp300.000</t>
+          <t>Rp175.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -6319,16 +6319,16 @@
         <v>64</v>
       </c>
       <c r="D20" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp3.794.000</t>
+          <t>Rp4.792.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp12.000.000</t>
+          <t>Rp12.360.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp12.310.000</t>
+          <t>Rp11.860.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp10.190.000</t>
+          <t>Rp11.290.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp16.531.000</t>
+          <t>Rp17.091.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp17.310.000</t>
+          <t>Rp17.770.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.825.000</t>
+          <t>Rp6.175.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp5.000.000</t>
+          <t>Rp6.500.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp25.000.000</t>
+          <t>Rp25.300.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.894.000</t>
+          <t>Rp9.389.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp850.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.235.000</t>
+          <t>Rp3.405.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp9.325.000</t>
+          <t>Rp9.625.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>85</v>
       </c>
       <c r="D36" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.175.000</t>
+          <t>Rp4.525.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>34</v>
       </c>
       <c r="D37" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp288.000</t>
+          <t>Rp864.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp16.900.000</t>
+          <t>Rp17.825.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>112</v>
       </c>
       <c r="D43" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp8.890.000</t>
+          <t>Rp9.115.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>174</v>
       </c>
       <c r="D44" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp29.100.000</t>
+          <t>Rp29.500.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.225.000</t>
+          <t>Rp5.525.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>88</v>
       </c>
       <c r="D5" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp5.950.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.030.000</t>
+          <t>Rp2.070.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.640.000</t>
+          <t>Rp6.150.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.180.000</t>
+          <t>Rp2.840.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.824.994</t>
+          <t>Rp2.949.994</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8445,12 +8445,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp540.000</t>
+          <t>Rp396.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp135.000</t>
+          <t>Rp99.000</t>
         </is>
       </c>
     </row>
@@ -8529,16 +8529,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp5.899.000</t>
+          <t>Rp6.458.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp18.980.000</t>
+          <t>Rp19.280.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.899.988</t>
+          <t>Rp5.024.988</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp415.000</t>
+          <t>Rp705.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp650.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.875.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.895.000</t>
+          <t>Rp2.390.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.140.000</t>
+          <t>Rp2.325.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp796.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-01.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-01.xlsx
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.783.000</t>
+          <t>Rp2.186.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.494.000</t>
+          <t>Rp2.629.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp4.480.000</t>
+          <t>Rp4.960.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp995.000</t>
+          <t>Rp1.891.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.530.985</t>
+          <t>Rp5.128.987</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp10.324.000</t>
+          <t>Rp9.224.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp320.000</t>
+          <t>Rp1.884.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>134</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp5.340.000</t>
+          <t>Rp5.640.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.365.000</t>
+          <t>Rp4.155.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp2.157.000</t>
+          <t>Rp2.595.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>168</v>
       </c>
       <c r="D22" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp12.525.000</t>
+          <t>Rp13.023.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp4.900.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.125.000</t>
+          <t>Rp4.125.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.920.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.879.000</t>
+          <t>Rp2.419.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.195.000</t>
+          <t>Rp2.735.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.730.000</t>
+          <t>Rp5.920.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp3.360.000</t>
+          <t>Rp3.780.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.510.000</t>
+          <t>Rp1.765.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>180</v>
       </c>
       <c r="D43" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp15.100.000</t>
+          <t>Rp16.600.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>180</v>
       </c>
       <c r="D44" t="n">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.150.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1939,16 +1939,16 @@
         <v>105</v>
       </c>
       <c r="D49" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp5.450.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp2.304.000</t>
+          <t>Rp2.880.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>60</v>
       </c>
       <c r="D54" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp1.408.000</t>
+          <t>Rp1.496.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>36</v>
       </c>
       <c r="D55" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp200.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.950.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp8.060.000</t>
+          <t>Rp8.160.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2463,14 +2463,14 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D66" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>90</v>
       </c>
       <c r="D67" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp8.344.000</t>
+          <t>Rp9.940.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>32</v>
       </c>
       <c r="D68" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp1.040.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>34</v>
       </c>
       <c r="D69" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp891.000</t>
+          <t>Rp1.089.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>176</v>
       </c>
       <c r="D70" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp1.743.000</t>
+          <t>Rp2.739.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>90</v>
       </c>
       <c r="D74" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp5.675.000</t>
+          <t>Rp6.325.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>45</v>
       </c>
       <c r="D77" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>120</v>
       </c>
       <c r="D78" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp4.900.000</t>
+          <t>Rp5.390.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>111</v>
       </c>
       <c r="D80" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp1.975.000</t>
+          <t>Rp3.475.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>80</v>
       </c>
       <c r="D81" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp3.188.000</t>
+          <t>Rp2.790.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -2993,16 +2993,16 @@
         <v>36</v>
       </c>
       <c r="D83" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp2.812.000</t>
+          <t>Rp3.062.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>80</v>
       </c>
       <c r="D88" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp1.842.000</t>
+          <t>Rp2.340.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>119</v>
       </c>
       <c r="D91" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp3.375.000</t>
+          <t>Rp3.755.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>34</v>
       </c>
       <c r="D95" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp1.375.000</t>
+          <t>Rp2.275.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>64</v>
       </c>
       <c r="D96" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp2.640.000</t>
+          <t>Rp2.860.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp2.670.000</t>
+          <t>Rp3.570.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.215.000</t>
+          <t>Rp1.053.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>127</v>
       </c>
       <c r="D3" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.317.000</t>
+          <t>Rp15.657.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp778.000</t>
+          <t>Rp2.334.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp13.250.000</t>
+          <t>Rp14.900.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp7.985.000</t>
+          <t>Rp8.775.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp6.650.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>63</v>
       </c>
       <c r="D25" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp770.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>60</v>
       </c>
       <c r="D27" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp5.982.000</t>
+          <t>Rp6.331.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp16.035.000</t>
+          <t>Rp16.375.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4408,16 +4408,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.525.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.890.000</t>
+          <t>Rp3.640.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>28</v>
       </c>
       <c r="D36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.094.000</t>
+          <t>Rp1.283.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4811,16 +4811,16 @@
         <v>64</v>
       </c>
       <c r="D42" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>80</v>
       </c>
       <c r="D48" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>84</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.550.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>54</v>
       </c>
       <c r="D51" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp7.200.000</t>
+          <t>Rp6.400.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp4.850.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>72</v>
       </c>
       <c r="D53" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp720.000</t>
+          <t>Rp2.160.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>64</v>
       </c>
       <c r="D62" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp9.000.000</t>
+          <t>Rp8.400.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>84</v>
       </c>
       <c r="D65" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp6.545.000</t>
+          <t>Rp7.245.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>144</v>
       </c>
       <c r="D66" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp15.500.000</t>
+          <t>Rp17.300.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>90</v>
       </c>
       <c r="D70" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp6.400.000</t>
+          <t>Rp7.900.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp20.955.000</t>
+          <t>Rp20.075.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.025.000</t>
+          <t>Rp2.650.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp35.850.000</t>
+          <t>Rp39.550.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.410.000</t>
+          <t>Rp4.710.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.890.000</t>
+          <t>Rp5.240.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp12.360.000</t>
+          <t>Rp12.010.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp11.860.000</t>
+          <t>Rp12.260.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp138.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp11.290.000</t>
+          <t>Rp12.615.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>102</v>
       </c>
       <c r="D9" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.442.000</t>
+          <t>Rp9.150.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp6.265.000</t>
+          <t>Rp6.823.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.175.000</t>
+          <t>Rp6.575.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6866,21 +6866,21 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp6.500.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rp88.000 - Rp325.000</t>
+          <t>Rp50.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -6897,16 +6897,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>42</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.001.000</t>
+          <t>Rp2.387.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp25.300.000</t>
+          <t>Rp22.200.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp10.600.000</t>
+          <t>Rp9.900.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp9.389.000</t>
+          <t>Rp8.094.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp3.650.000</t>
+          <t>Rp4.400.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7235,24 +7235,24 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D29" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.160.000</t>
+          <t>Rp5.900.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rp140.000 - Rp860.000</t>
+          <t>Rp140.000 - Rp1.000.000</t>
         </is>
       </c>
     </row>
@@ -7269,16 +7269,16 @@
         <v>80</v>
       </c>
       <c r="D30" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.405.000</t>
+          <t>Rp3.690.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp9.625.000</t>
+          <t>Rp9.875.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>102</v>
       </c>
       <c r="D35" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.420.000</t>
+          <t>Rp1.710.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>85</v>
       </c>
       <c r="D36" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.525.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>34</v>
       </c>
       <c r="D37" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp864.000</t>
+          <t>Rp1.440.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp17.825.000</t>
+          <t>Rp18.375.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>112</v>
       </c>
       <c r="D40" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.798.000</t>
+          <t>Rp1.998.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>80</v>
       </c>
       <c r="D41" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>64</v>
       </c>
       <c r="D42" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.160.000</t>
+          <t>Rp2.560.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>112</v>
       </c>
       <c r="D43" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp9.115.000</t>
+          <t>Rp9.645.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>102</v>
       </c>
       <c r="D45" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp410.000</t>
+          <t>Rp860.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>98</v>
       </c>
       <c r="D48" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp7.610.000</t>
+          <t>Rp8.800.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.525.000</t>
+          <t>Rp5.700.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7971,16 +7971,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.925.000</t>
+          <t>Rp2.395.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.070.000</t>
+          <t>Rp2.330.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.150.000</t>
+          <t>Rp6.660.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.840.000</t>
+          <t>Rp4.820.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp3.995.000</t>
+          <t>Rp4.535.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.949.994</t>
+          <t>Rp3.274.993</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp396.000</t>
+          <t>Rp792.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp640.000</t>
+          <t>Rp960.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.470.000</t>
+          <t>Rp2.130.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp5.024.988</t>
+          <t>Rp4.624.990</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp3.930.000</t>
+          <t>Rp4.215.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp705.000</t>
+          <t>Rp1.140.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.900.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.875.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>144</v>
       </c>
       <c r="D36" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.007.000</t>
+          <t>Rp5.497.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp970.000</t>
+          <t>Rp1.984.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-01.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-01.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.840.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp1.799.000</t>
+          <t>Rp1.898.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.128.987</t>
+          <t>Rp5.572.987</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>134</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp5.640.000</t>
+          <t>Rp5.790.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.155.000</t>
+          <t>Rp4.575.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.900.000</t>
+          <t>Rp4.750.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.735.000</t>
+          <t>Rp2.895.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.220.000</t>
+          <t>Rp3.612.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1781,19 +1781,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D44" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>36</v>
       </c>
       <c r="D60" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp992.000</t>
+          <t>Rp1.091.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp1.355.000</t>
+          <t>Rp1.430.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>90</v>
       </c>
       <c r="D90" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp2.640.000</t>
+          <t>Rp2.880.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp3.570.000</t>
+          <t>Rp3.770.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp8.775.000</t>
+          <t>Rp9.170.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>68</v>
       </c>
       <c r="D54" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp7.385.000</t>
+          <t>Rp7.680.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp20.075.000</t>
+          <t>Rp20.267.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.710.000</t>
+          <t>Rp5.210.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp1.660.000</t>
+          <t>Rp1.779.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.240.000</t>
+          <t>Rp4.890.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp138.000</t>
+          <t>Rp237.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>102</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp9.150.000</t>
+          <t>Rp9.400.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp22.200.000</t>
+          <t>Rp22.800.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>102</v>
       </c>
       <c r="D45" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp860.000</t>
+          <t>Rp1.310.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp5.875.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.660.000</t>
+          <t>Rp6.810.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp4.535.000</t>
+          <t>Rp4.935.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.274.993</t>
+          <t>Rp3.399.993</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp5.610.000</t>
+          <t>Rp5.855.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
